--- a/data/03_output/evaluaciones/auditoria_manual_3_BM25.xlsx
+++ b/data/03_output/evaluaciones/auditoria_manual_3_BM25.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Cómo se clasifican los tipos de crédito de la Cartera Crediticia de Consumo no Revolvente para el cálculo de reservas?</t>
+          <t>¿Para consumo no revolvente cómo se define el pago realizado?</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,17 +464,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>## Capítulo V Bis  
-Metodologías Generales Estándar por tipo de cartera de crédito  
-Sección Primera  
-De la Cartera Crediticia de Consumo  
-Apartado A  
-De la Metodología General Estándar para la calificación de Cartera Crediticia de Consumo no Revolvente</t>
+          <t>### Definiciones  
+Aval.- Contrato mediante el cual, la entidad sustenta la capacidad crediticia de determinado acreditado mediante la promesa de pago de la obligación en caso de incumplimiento.  
+Pág. 57  
+En el contrato que da origen al aval, se define la eventualidad que generará el posible compromiso de pago, por lo que hasta que dicha eventualidad no se materialice, los avales representan únicamente un compromiso.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ABCD (B) | A los créditos que sean otorgados a personas físicas y cuyo destino sea la adquisición de bienes de consumo duradero</t>
+          <t>Monto correspondiente a la suma de los pagos realizados por el acreditado en el Periodo de Facturación</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -653,7 +651,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>¿Cómo pueden las instituciones financieras utilizar las garantías reales financieras para reducir las reservas preventivas según el Artículo 97 Bis 6?</t>
+          <t>¿Qué se consideraría un crédito personal?</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -661,12 +659,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>### Artículo 97 Bis 6.- Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas derivadas de la calificación de cartera de los créditos a los que se refiere la presente sección. Para tal efecto, emplearán</t>
+          <t>La determinación de la utilidad o pérdida por renegociación a que se refiere el párrafo 80, no resultará aplicable a las tarjetas de crédito, a los créditos a que se refiere el párrafo 59, o bien a los créditos con riesgo de crédito etapa 3.  
+Si la entidad renueva un crédito, se considerará que existe un nuevo crédito por lo que se deberá dar de baja el crédito anterior en el caso de una renovación total.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras</t>
+          <t>A los créditos que sean cobrados por la Institución por cualquier medio de pago distinto de la cuenta de nómina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -731,7 +730,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>¿Qué enfoques pueden adoptar las instituciones para el cálculo de reservas preventivas y cuáles son sus requisitos?</t>
+          <t>¿Qué se entiendo por saldo a pagar?</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -739,13 +738,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Las Instituciones, podrán optar por alguno de los enfoques siguientes:  
-I. El Enfoque Estándar, el cual resulta aplicable a todas las carteras consideradas en la definición de Cartera Crediticia contenida en el Artículo 1 de las presentes disposiciones. Las Instituciones que adopten este enfoque para el cálculo de sus reservas preventivas deberán sujetarse a los requisitos y procedimientos contenidos dentro del Capítulo V Bis.</t>
+          <t>El castigo a que se refiere el párrafo anterior se realizará cancelando el saldo del crédito, determinado como incobrable por la administración, contra la estimación preventiva para riesgos crediticios. Cuando el crédito a castigar exceda el saldo de su estimación asociada, antes de efectuar el castigo, dicha estimación se deberá incrementar hasta por el monto de la diferencia.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Las Instituciones, podrán optar por alguno de los enfoques siguientes: I. El Enfoque Estándar... II. El Enfoque Interno...</t>
+          <t>Importe exigible de la deuda a la fecha de corte en la cual inicia el Periodo de Pago que el acreditado tiene por pagar a la Institución</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -758,7 +756,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>¿Cómo se determina la Probabilidad de Incumplimiento para créditos clasificados como "B" en la Cartera Crediticia de Consumo no Revolvente?</t>
+          <t>¿Cómo se determina la reservas para los créditos en etapa 2?</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -766,15 +764,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>### Artículo 91 Bis 1.- La Probabilidad de Incumplimiento de los créditos clasificados como “B, A, N, P u O” conforme al Artículo 91 Bis de las presentes disposiciones, se determinará de acuerdo con las fracciones I a V siguientes, según corresponda:  
-I. La Probabilidad de Incumplimiento de los créditos de la Cartera Crediticia de Consumo no Revolvente clasificados como “B” deberá obtenerse conforme a lo siguiente:  
-a) Si $ATR_{i}^{B} &amp;gt; 3$ o cuando el crédito se encuentre en etapa 3:  
-$$</t>
+          <t>Los cálculos requeridos para obtener las reservas para la vida completa de los créditos deberán realizarse considerando cuatro decimales.  
+El monto de reservas para los créditos en etapa 2 será el resultado de:  
+$$
+\ Reservas\ Etapa\ 2_i = \max\left(\text{Reservas\ Vida\ Completa}_i, PI_i^X \times SP_i^X \times EI_i^X\right)
+$$  
+El monto total de reservas a constituir por la Institución para esta cartera, será igual a la sumatoria de las reservas de cada crédito.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>La Probabilidad de Incumplimiento de los créditos de la Cartera Crediticia de Consumo no Revolvente clasificados como “B” deberá obtenerse conforme a lo siguiente: a) Si $ATR_{i}^{B} &gt; 3$ o cuando el crédito se encuentre en etapa 3: PI_{i}^{B} = 100%</t>
+          <t>Reservas\ Etapa\ 2_i = \max\left(\text{Reservas\ Vida\ Completa}_i, PI_i^X \times SP_i^X \times EI_i^X\right)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>¿Qué criterios deben seguir las instituciones para migrar un crédito entre etapas de riesgo?</t>
+          <t>¿Se pueden reportar tasas de interés en cero?</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -824,12 +824,15 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deberán reconocerse como cartera de crédito con riesgo de crédito etapa 3, aquellos créditos respecto de los cuales las entidades cuenten con algún elemento para determinar que deben migrar de etapa 1 o 2 a etapa 3, de conformidad con lo dispuesto en las Disposiciones.</t>
+          <t># Modificaciones a las tasas de interés  
+### Artículo 11.- Las tasas de interés pactadas en los Depósitos podrán modificarse conforme a lo siguiente:  
+I. En los Depósitos a la vista y de ahorro, las Instituciones podrán reservarse el derecho de modificar la tasa, y
+II. En los Depósitos retirables en días preestablecidos, las tasas solo podrán modificarse los Días en que el depositante pueda efectuar retiros.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los criterios bajo los cuales las Instituciones podrán realizar dicha migración deberán estar formalizados dentro de los manuales de políticas y procedimientos de la Institución y deberán ser aplicados de forma consistente.</t>
+          <t>En casos donde la tasa de interés anual sea igual a cero, se deberá utilizar un valor fijo de 0.00001%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -842,7 +845,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>¿Cómo se determina la Probabilidad de Incumplimiento para créditos con ACT_i ≤ 3?</t>
+          <t>¿Cuándo no exista información del acreditado en las sociedades de información crediticia que factor de riesgo se aplica?</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -850,24 +853,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Reservas Etapa 2i = Max(Reservas Vida Completa_i, PI_i × SP_i × EI_i)  
-III. Para estimar las reservas será necesario obtener la Probabilidad de Incumplimiento, la Severidad de la Pérdida y la Exposición al Incumplimiento de acuerdo a lo siguiente:  
-a) Probabilidad de Incumplimiento:  
-1. Si ACT i &amp;gt; 3 o cuando el crédito se encuentra en etapa 3, entonces:  
-$$
-PI_i = 100\%
-$$  
-2. Si ACT i ≤ 3 entonces:  
-$$
-PI_i = \frac{1}{1 + e^{-Z_i}}
-$$  
-En donde:  
-$$</t>
+          <t>Cuando no exista información del acreditado en las sociedades de información crediticia autorizadas y no se cuente con evidencia dentro de la Institución de que el acreditado cuenta con atrasos en alguno de los créditos otorgados por la propia Institución, para realizar el cálculo de la variable $MESES_{i}^{B}$ las Instituciones asignarán el valor de 13. En caso de que se cuente con evidencia de que el acreditado cuenta con atrasos en alguno de los créditos otorgados por la propia Institución,</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PI_i = \frac{1}{1 + e^{-Z_i}}</t>
+          <t>Cuando no exista información del acreditado en las sociedades de información crediticia autorizadas, las Instituciones para realizar el cálculo de las variables...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -880,91 +871,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>¿Cómo pueden las instituciones financieras reducir las reservas preventivas a través del reconocimiento de garantías?</t>
+          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Cobertura de Liquidez y cómo debe expresarse el resultado porcentual?</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
-        <is>
-          <t>Adicionalmente, la Comisión Nacional Bancaria y de Valores, en protección de los intereses del público ahorrador, podrá ordenar a las instituciones de crédito, como medida correctiva, la constitución de reservas preventivas cuando detecte una inadecuada valuación o una incorrecta estimación en términos del párrafo anterior. Dichas reservas serán adicionales a las que las instituciones de crédito tengan la obligación de constituir en términos de las disposiciones aplicables, debiendo escuchar</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Q17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>¿Qué tipos de garantías son reconocidos para la estimación de la Severidad de la Pérdida de los créditos?</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>### Artículo 97 Bis 6.- Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas derivadas de la calificación de cartera de los créditos a los que se refiere la presente sección. Para tal efecto, emplearán</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Q18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>¿En qué condiciones deben las instituciones aplicar el apartado E para calcular sus reservas?</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>54. En el Anexo 2 se incluyen plantillas de reporte de muestra. Como se señaló anteriormente, las herramientas aplican a bancos internacionalmente activos. Los supervisores nacionales determinarán si otros bancos deben aplicar los requerimientos de reporte. Los bancos también deben acordar con sus supervisores el alcance de aplicación y los arreglos de reporte entre autoridades de origen y de acogida.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>emplearán el presente apartado siempre que calculen sus reservas con la metodología de calificación de cartera a la que se refiere esta sección</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Q19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Cobertura de Liquidez y cómo debe expresarse el resultado porcentual?</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
         <is>
           <t>El Coeficiente de Cobertura de Liquidez será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.  
 $$
@@ -972,135 +885,135 @@
 $$</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>El Coeficiente de Cobertura de Liquidez será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Q20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>¿Cómo se determina el flujo de salida contingente por operaciones con instrumentos financieros derivados?</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Las Instituciones que no puedan identificar el flujo acumulado de garantía neto al que se refiere el inciso a) anterior deberán estimar el flujo de salida contingente por operaciones con instrumentos financieros derivados utilizando únicamente lo establecido en el inciso b).</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Las Instituciones deberán calcular el flujo de salida contingente por operaciones con instrumentos financieros derivados como el máximo valor absoluto de la suma de los montos referidos en los incisos a) y b) siguientes</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Q21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>¿Cómo se calcula el flujo total de entrada de efectivo?</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>V. El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el  
 75 por ciento del flujo total de salida de efectivo calculado conforme el artículo 11 de las presentes disposiciones.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el 75 por ciento del flujo total de salida de efectivo</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>¿Qué factor de salida se aplica a depósitos en cuentas transaccionales de personas físicas cubiertos por el IPAB?</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>## Cuentahabientes  
 ### Artículo 8º.- Las Instituciones podrán abrir cuentas de Depósito denominadas en moneda nacional a personas físicas y morales. Las cuentas especiales para el ahorro y las cuentas de los niveles 1 y 2 de los Depósitos a la vista únicamente podrán abrirse a personas físicas.  
 No obstante lo anterior, las Instituciones de Banca de Desarrollo solo podrán abrir cuentas a personas físicas cuando sus leyes orgánicas así lo permitan.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>I.1.2.1 Monto que no excede el límite establecido en la Ley para la Protección al Ahorro Bancario para las operaciones pasivas garantizadas por el IPAB</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Q23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>¿Cómo se registran las operaciones de compra-venta fecha valor para calcular el coeficiente de cobertura de liquidez?</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Operacionales que se reconoce en el cálculo del coeficiente de cobertura de liquidez como un flujo de entrada.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Compensar para cada operación de compra venta de títulos pactada a una fecha valor, la parte activa y pasiva de la misma operación e incluir el monto resultante como flujo de entrada</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Q24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Financiamiento Estable Neto y cómo debe expresarse el resultado porcentual?</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.  
 $$
@@ -1108,55 +1021,55 @@
 $$</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Q25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>¿Con qué periodicidad debe reportarse el CFEN al Banco de México y a qué fecha de cálculo corresponde?</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>b) el saldo inicial de efectivo y equivalentes de efectivo debe convertirse al tipo de cambio de cierre de jornada a la fecha de cierre del periodo actual, que publique el Banco de México en la referida página de Internet, y  
 c) el saldo final de efectivo y equivalentes de efectivo debe convertirse al tipo de cambio de cierre de jornada a la fecha de cierre del periodo actual, que publique el Banco de México en la referida página de Internet.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto que corresponda al último Día Hábil de cada mes deberá reportarse durante los primeros dieciséis Días Hábiles del mes inmediato siguiente.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Q26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>¿Qué se entiende por Monto de Financiamiento Estable Disponible para efectos del CFEN?</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>ANEXO 6
 Determinación del Monto de Financiamiento Estable Disponible  
@@ -1164,83 +1077,83 @@
 i. Se incluirán todas sus operaciones pasivas y su capital, incluyendo aquellas operaciones pasivas contingentes registradas en cuentas de orden.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Monto de Financiamiento Estable Disponible: al monto que resulte de sumar los pasivos y capital señalados en el Anexo 6 de las presentes disposiciones</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Q27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>¿Qué se entiende por Monto de Financiamiento Estable Requerido para efectos del CFEN?</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t># ANEXO 7  
 Monto de Financiamiento Estable Requerido para activos no restringidos y otras operaciones  
 Las Instituciones, para determinar el Monto de Financiamiento Estable Requerido para activos no restringidos y otras operaciones, deberán observar lo siguiente:</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Monto de Financiamiento Estable Requerido: al monto que resulte de sumar: (i) los activos no restringidos y otras operaciones señaladas en el Anexo 7 de las presentes disposiciones</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Q28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>¿Qué factor de financiamiento estable disponible se asigna al capital fundamental, capital básico no fundamental y pasivos con plazo residual igual o mayor a un año?</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>ii) Un coeficiente de capital básico igual o mayor al 6 por ciento, más el suplemento de conservación de capital que le corresponda, y
 iii) Un coeficiente de capital fundamental igual o mayor al 4.5 por ciento, más el suplemento de conservación de capital que le corresponda.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Los factores para la determinación del financiamiento estable disponible serán: I. Pasivos y capital con factor del 100% A. Capital fundamental</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Q29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>¿Cuál es la definición de liquidez intradía según las herramientas de monitoreo del Comité de Basilea?</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>IV. Escenarios de tensión de liquidez intradía ... 8
 V. Alcance de aplicación ... 10
@@ -1252,82 +1165,82 @@
 Herramientas de monitoreo para la gestión de la liquidez intradía - traducción al español</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Liquidez intradía: fondos a los que se puede acceder durante el día hábil, usualmente para permitir que los bancos realicen pagos en tiempo real;</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Q30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>¿Cuáles son las principales fuentes propias de liquidez intradía que puede utilizar un banco durante el día hábil?</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Escenarios de tensión  
 (i) Tensión financiera propia: el banco sufre, o se percibe que sufre, un evento de tensión  
 30. Para un participante directo, la tensión financiera y/u operativa propia puede provocar que las contrapartes difieran pagos y/o retiren líneas de crédito intradía. Esto, a su vez, puede ocasionar que el banco tenga que financiar una mayor parte de sus pagos con sus propias fuentes de liquidez intradía para evitar diferir sus propios pagos.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>(i) Fuentes Fuentes propias - Saldos de reserva en el banco central; - Colateral pignorado con el banco central o con sistemas auxiliares</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Q31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>¿Cómo se define un escenario de tensión de contraparte?</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>38. Para el escenario de tensión de un banco cliente, los bancos que prestan servicios de corresponsalía bancaria deben considerar el impacto probable que este escenario tendría sobre el valor de los pagos realizados en nombre de sus clientes y sobre las líneas de crédito intradía otorgadas a sus clientes.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>(ii) Tensión de contraparte: una contraparte importante sufre un evento de tensión intradía que le impide realizar pagos</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Q32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>¿Cómo se calcula el uso máximo diario de liquidez intradía a partir de la posición neta acumulada de pagos enviados y recibidos?</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Figura 1. Uso máximo diario de liquidez intradía  
 Herramientas de monitoreo para la gestión de la liquidez intradía - traducción al español
@@ -1335,39 +1248,39 @@
 La figura ilustra una trayectoria de posición neta acumulada durante el día: el mayor valor positivo corresponde a la posición neta acumulada positiva más alta, mientras que el punto más bajo corresponde a la mayor posición neta acumulada negativa. En el ejemplo, el uso de liquidez intradía equivale a 10 unidades.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>(i) Uso máximo diario de liquidez intradía 13. Esta herramienta permitirá a los supervisores monitorear el uso de liquidez intradía de un banco en condiciones normales.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Q33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>¿Qué son las obligaciones con horario específico y por qué su incumplimiento puede generar riesgo financiero o reputacional?</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>## (iv) Obligaciones con horario específico  
 22. Esta herramienta permitirá a los supervisores comprender mejor las obligaciones con horario específico de un banco. La falta de liquidación oportuna de estas obligaciones podría generar una penalización financiera, daño reputacional para el banco o pérdida de negocio futuro.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>(iv) Obligaciones con horario específico 22. Esta herramienta permitirá a los supervisores comprender mejor las obligaciones con horario específico de un banco.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
